--- a/course_enrollment_forms/006_nise_stim_course_registration--course_enrollment_forms.xlsx
+++ b/course_enrollment_forms/006_nise_stim_course_registration--course_enrollment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>course_code</t>
+          <t>course code</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>course_title</t>
+          <t>course title</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>status1</t>
+          <t>status_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>status1</t>
+          <t>Status 1</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>status2</t>
+          <t>status_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>status2</t>
+          <t>Status 2</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>status1</t>
+          <t>status_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>status1</t>
+          <t>Status 1</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>status2</t>
+          <t>status_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>status2</t>
+          <t>Status 2</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>up2_1</t>
+          <t>up2 1</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>up2_2</t>
+          <t>up2 2</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>status1</t>
+          <t>status_1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>status1</t>
+          <t>Status 1</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>status2</t>
+          <t>status_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>status2</t>
+          <t>Status 2</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>status1</t>
+          <t>status_1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>status1</t>
+          <t>Status 1</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>status2</t>
+          <t>status_2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>status2</t>
+          <t>Status 2</t>
         </is>
       </c>
     </row>
